--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:36:35+00:00</t>
+    <t>2026-06-22T13:39:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -531,7 +531,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant</t>
+    <t>External Identifiers for this procedure</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:39:21+00:00</t>
+    <t>2026-07-22T12:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Procedure|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/procedure-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -349,7 +349,7 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
+    <t>Language of the procedure</t>
   </si>
   <si>
     <t>The base language in which the resource is written.</t>
@@ -381,7 +381,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>Textual representation of the procedure</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -449,6 +449,30 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>Procedure.extension:recorded</t>
+  </si>
+  <si>
+    <t>recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Procedure.recorded|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Date when the procedure was recorded</t>
+  </si>
+  <si>
+    <t>R5: `Procedure.recorded` (new:dateTime)</t>
+  </si>
+  <si>
+    <t>Element `Procedure.recorded` has a context of Procedure based on following the parent source element upwards and mapping to `Procedure`.
+Element `Procedure.recorded` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Procedure.extension:priority</t>
   </si>
   <si>
@@ -465,10 +489,6 @@
     <t>Extension permettant d'indiquer la priorité clinique de l'acte.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Procedure.extension:approachBodySite</t>
   </si>
   <si>
@@ -531,7 +551,7 @@
 </t>
   </si>
   <si>
-    <t>External Identifiers for this procedure</t>
+    <t>Identifier for the procedure</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
@@ -735,7 +755,7 @@
     <t>Code d'acte</t>
   </si>
   <si>
-    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
+    <t>Identification of the procedure or recording of "absence of relevant procedures" or of "procedures unknown".</t>
   </si>
   <si>
     <t>Aussi utilisé pour indiquer qu'il n'y a pas d'acte ou qu'on ne sait pas s'il y en a.
@@ -854,7 +874,7 @@
 </t>
   </si>
   <si>
-    <t>Who recorded the procedure</t>
+    <t>The person or organization who recorded the procedure</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -869,7 +889,7 @@
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t>Person who asserts this procedure</t>
+    <t>The person or organization who asserts the procedure</t>
   </si>
   <si>
     <t>Individual who is making the procedure statement.</t>
@@ -978,7 +998,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1006,7 +1026,7 @@
     <t>Procedure.performer.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1047,7 +1067,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Coded reason procedure performed</t>
+    <t>Why the procedure was performed (code)</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -1074,7 +1094,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/condition-eu-core|2.0.0|Observation|4.0.1|http://hl7.eu/fhir/base/StructureDefinition/procedure-eu-core|2.0.0|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1097,7 +1117,7 @@
     <t>Localisation anatomique</t>
   </si>
   <si>
-    <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
+    <t>Anatomical location which is the focus of the problem.</t>
   </si>
   <si>
     <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
@@ -1109,16 +1129,153 @@
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+eu-bodysite-1:Either a body site code or a reference to a BodyStructure resource SHALL be used, but not both. {(coding.empty() and text.empty()) or extension('http://hl7.org/fhir/StructureDefinition/bodySite').empty()}</t>
+  </si>
+  <si>
     <t>.targetSiteCode</t>
   </si>
   <si>
     <t>OBX-20</t>
   </si>
   <si>
+    <t>Procedure.bodySite.id</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite.id</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension.id</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite.url</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/bodyStructure-eu-core|2.0.0)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>The result of procedure</t>
+    <t>Outcome of the procedure</t>
   </si>
   <si>
     <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
@@ -1158,7 +1315,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Complication following the procedure</t>
+    <t>Complications that occurred during the procedure (code)</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -1179,11 +1336,11 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/condition-eu-core|2.0.0)
 </t>
   </si>
   <si>
-    <t>A condition that is a result of the procedure</t>
+    <t>Complications that occurred during the procedure (details)</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -1217,7 +1374,7 @@
 </t>
   </si>
   <si>
-    <t>Additional information about the procedure</t>
+    <t>Additional information about the procedure.</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -1235,7 +1392,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Manipulated, implanted, or removed device</t>
+    <t>Device implanted, removed or otherwise manipulated</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -1290,7 +1447,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Medication|4.0.1|Substance|4.0.1)
+    <t xml:space="preserve">Reference(Device|4.0.1|http://hl7.eu/fhir/base/StructureDefinition/medication-eu-core|2.0.0|Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1313,7 +1470,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Coded items used during the procedure</t>
+    <t>Device used to perform the procedure (code)</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>
@@ -1635,10 +1792,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.10546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.26953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1648,7 +1805,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="115.03125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1666,7 +1823,7 @@
     <col min="26" max="26" width="52.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2743,7 +2900,9 @@
       <c r="M10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2801,7 +2960,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2821,13 +2980,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>78</v>
@@ -2837,7 +2996,7 @@
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>78</v>
@@ -2849,13 +3008,13 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2915,7 +3074,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>139</v>
@@ -2935,13 +3094,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>78</v>
@@ -2951,7 +3110,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -2963,13 +3122,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3029,7 +3188,7 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>139</v>
@@ -3049,46 +3208,44 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
         <v>161</v>
       </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
@@ -3136,7 +3293,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3154,7 +3311,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3165,14 +3322,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3185,25 +3342,25 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3252,7 +3409,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3264,27 +3421,27 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3307,16 +3464,20 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -3364,7 +3525,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3379,16 +3540,16 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -3419,17 +3580,15 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
         <v>182</v>
       </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3496,7 +3655,7 @@
         <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3507,14 +3666,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3533,15 +3692,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3590,7 +3751,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3608,7 +3769,7 @@
         <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3619,14 +3780,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3645,17 +3806,15 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3704,7 +3863,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3719,10 +3878,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3733,33 +3892,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>200</v>
@@ -3794,13 +3953,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3818,13 +3977,13 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
@@ -3833,13 +3992,13 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3847,18 +4006,18 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>88</v>
@@ -3867,22 +4026,22 @@
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3908,13 +4067,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3932,10 +4091,10 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>88</v>
@@ -3947,13 +4106,13 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -3961,14 +4120,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3987,15 +4146,17 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4020,31 +4181,31 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4059,13 +4220,13 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>224</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4073,18 +4234,18 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4099,20 +4260,16 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4136,11 +4293,13 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>78</v>
@@ -4158,7 +4317,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4173,28 +4332,28 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4213,16 +4372,20 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4246,13 +4409,11 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -4270,10 +4431,10 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>88</v>
@@ -4285,32 +4446,32 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
@@ -4325,17 +4486,15 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4384,10 +4543,10 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
@@ -4399,24 +4558,24 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4439,16 +4598,16 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4498,7 +4657,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4513,24 +4672,24 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4538,7 +4697,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4553,15 +4712,17 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4610,7 +4771,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4625,16 +4786,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27">
@@ -4665,13 +4826,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4740,10 +4901,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4751,10 +4912,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4765,7 +4926,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4777,7 +4938,7 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>278</v>
@@ -4834,13 +4995,13 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
@@ -4849,13 +5010,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4877,7 +5038,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4886,7 +5047,7 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>283</v>
@@ -4946,22 +5107,22 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>287</v>
@@ -4982,14 +5143,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -5001,17 +5162,15 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5060,25 +5219,25 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5089,14 +5248,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5109,26 +5268,24 @@
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5176,7 +5333,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5194,7 +5351,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5205,43 +5362,45 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>300</v>
+        <v>167</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5266,63 +5425,63 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>301</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>304</v>
+        <v>131</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5330,7 +5489,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5345,17 +5504,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>307</v>
+        <v>217</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5380,13 +5539,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5404,10 +5563,10 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5419,24 +5578,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5444,7 +5603,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5456,20 +5615,20 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5518,10 +5677,10 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>88</v>
@@ -5533,16 +5692,16 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="35">
@@ -5570,7 +5729,7 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>322</v>
@@ -5653,7 +5812,7 @@
         <v>326</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5661,10 +5820,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5675,7 +5834,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5687,7 +5846,7 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>211</v>
+        <v>328</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>329</v>
@@ -5695,10 +5854,10 @@
       <c r="M36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5722,13 +5881,13 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>333</v>
+        <v>78</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5746,13 +5905,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5761,13 +5920,13 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5775,10 +5934,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5801,16 +5960,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5836,13 +5995,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -5860,7 +6019,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5875,13 +6034,13 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5915,16 +6074,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5950,11 +6109,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -5987,24 +6148,24 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6015,7 +6176,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6027,16 +6188,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6062,55 +6223,53 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Y39" s="2"/>
+      <c r="Z39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z39" t="s" s="2">
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AA39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="40">
@@ -6129,7 +6288,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6141,17 +6300,15 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6200,25 +6357,25 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6229,14 +6386,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6255,16 +6412,16 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>367</v>
+        <v>166</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6290,31 +6447,31 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>368</v>
+        <v>78</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>78</v>
+        <v>360</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>297</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6326,13 +6483,13 @@
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6343,12 +6500,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6357,7 +6516,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6369,18 +6528,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6428,7 +6585,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>297</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6440,13 +6597,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6457,10 +6614,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6471,7 +6628,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6483,13 +6640,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>377</v>
+        <v>290</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
+        <v>291</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6516,13 +6673,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6540,25 +6697,25 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6569,10 +6726,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6583,7 +6740,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6595,13 +6752,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>383</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>135</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6640,19 +6797,19 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>78</v>
+        <v>360</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>297</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6664,27 +6821,27 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6692,10 +6849,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -6707,22 +6864,24 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>277</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>78</v>
@@ -6764,25 +6923,25 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>392</v>
+        <v>131</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6793,10 +6952,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6804,7 +6963,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -6819,13 +6978,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>283</v>
+        <v>379</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>284</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>285</v>
+        <v>381</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6876,7 +7035,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>286</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6885,16 +7044,16 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>287</v>
+        <v>131</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -6905,14 +7064,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6928,21 +7087,23 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>385</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6990,7 +7151,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>291</v>
+        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7002,62 +7163,62 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>287</v>
+        <v>391</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>293</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>289</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>294</v>
+        <v>394</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>160</v>
+        <v>396</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>161</v>
+        <v>397</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7106,39 +7267,39 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>296</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>131</v>
+        <v>399</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7158,18 +7319,20 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7194,13 +7357,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7218,7 +7381,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7236,7 +7399,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7247,10 +7410,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7258,10 +7421,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7273,15 +7436,17 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7330,13 +7495,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -7348,7 +7513,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7359,10 +7524,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7385,20 +7550,18 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>217</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7422,13 +7585,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -7446,7 +7609,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7464,7 +7627,7 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7475,10 +7638,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7501,18 +7664,18 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>211</v>
+        <v>422</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7536,13 +7699,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7560,7 +7723,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7578,12 +7741,1144 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:47:59+00:00</t>
+    <t>2026-07-22T12:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:55:33+00:00</t>
+    <t>2026-07-23T09:09:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -814,7 +814,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:09:32+00:00</t>
+    <t>2026-07-31T15:05:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T15:05:17+00:00</t>
+    <t>2026-08-03T08:32:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -793,7 +793,7 @@
 </t>
   </si>
   <si>
-    <t>Patient concerné</t>
+    <t>Who the procedure was performed on</t>
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
